--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_333_R34.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_333_R34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9643</v>
+        <v>7.1</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1906</v>
+        <v>7.1919</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2263</v>
+        <v>-0.0919</v>
       </c>
       <c r="G2" t="n">
         <v>5.1782</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1445</v>
+        <v>2.2802</v>
       </c>
       <c r="T2" t="n">
-        <v>2.67</v>
+        <v>1.6713</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4745</v>
+        <v>0.6089</v>
       </c>
       <c r="V2" t="n">
         <v>-1.7501</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6341</v>
+        <v>4.1078</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4681</v>
+        <v>3.1771</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1659</v>
+        <v>0.9307</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2841</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>0.8738</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7986</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6014</v>
+        <v>0.3662</v>
       </c>
       <c r="V3" t="n">
         <v>2.8223</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1831</v>
+        <v>1.8379</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3997</v>
+        <v>1.0209</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7834</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>1.5117</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6199</v>
+        <v>1.2746</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2715</v>
+        <v>0.8927</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3484</v>
+        <v>0.382</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2525</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8703</v>
+        <v>1.4529</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5137</v>
+        <v>2.7469</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6434</v>
+        <v>-1.2941</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4778</v>
+        <v>-0.7493</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0394</v>
+        <v>0.5625</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4384</v>
+        <v>-1.3118</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1777</v>
+        <v>0.2376</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1041</v>
+        <v>1.3856</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0736</v>
+        <v>-1.148</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3001</v>
+        <v>-0.9869</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3648</v>
+        <v>-0.1638</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="R5" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4673</v>
+        <v>1.0398</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3566</v>
+        <v>0.9164</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1107</v>
+        <v>0.1235</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.0748</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7886</v>
+        <v>3.2166</v>
       </c>
       <c r="X5" t="n">
         <v>-2.2862</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.144</v>
+        <v>0.4389</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0174</v>
+        <v>1.8807</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1614</v>
+        <v>-1.4418</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.004</v>
+        <v>2.4778</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.8305</v>
+        <v>2.0394</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8265</v>
+        <v>0.4384</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9564</v>
+        <v>2.1777</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.2078</v>
+        <v>2.1041</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2514</v>
+        <v>0.0736</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0476</v>
+        <v>0.3001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6227</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4248</v>
+        <v>0.3648</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2381</v>
+        <v>1.0359</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1889</v>
+        <v>0.7235</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0492</v>
+        <v>0.3123</v>
       </c>
       <c r="V6" t="n">
-        <v>1.214</v>
+        <v>-3.0748</v>
       </c>
       <c r="W6" t="n">
-        <v>1.214</v>
+        <v>-0.7886</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0238</v>
+        <v>0.1947</v>
       </c>
       <c r="E7" t="n">
-        <v>1.654</v>
+        <v>0.1005</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6301</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7493</v>
+        <v>-2.004</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5625</v>
+        <v>-2.8305</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3118</v>
+        <v>0.8265</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2376</v>
+        <v>-0.9564</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3856</v>
+        <v>-2.2078</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.148</v>
+        <v>1.2514</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9869</v>
+        <v>-1.0476</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.6227</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1638</v>
+        <v>-0.4248</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3892</v>
+        <v>0.2888</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1766</v>
+        <v>0.3068</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2126</v>
+        <v>-0.018</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9304</v>
+        <v>1.214</v>
       </c>
       <c r="W7" t="n">
-        <v>3.2166</v>
+        <v>1.214</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7157</v>
+        <v>-0.6597</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1107</v>
+        <v>0.1133</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.605</v>
+        <v>-0.773</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0805</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5091</v>
+        <v>0.5652</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2284</v>
+        <v>0.4525</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2807</v>
+        <v>0.1127</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5361</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9549</v>
+        <v>-0.669</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5965</v>
+        <v>-0.4785</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3585</v>
+        <v>-0.1904</v>
       </c>
       <c r="G9" t="n">
         <v>0.1083</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5091</v>
+        <v>-0.2232</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1357</v>
+        <v>0.0323</v>
       </c>
       <c r="V9" t="n">
         <v>0.1418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7595</v>
+        <v>-1.2488</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3267</v>
+        <v>-0.7488</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4328</v>
+        <v>-0.5</v>
       </c>
       <c r="G10" t="n">
         <v>-2.011</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7486</v>
+        <v>-0.2379</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9709</v>
+        <v>-0.393</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2223</v>
+        <v>0.1551</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.4414</v>
+        <v>-8.113</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.97</v>
+        <v>-6.3055</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4714</v>
+        <v>-1.8075</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1472</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7196</v>
+        <v>-0.3912</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1202</v>
+        <v>-0.4558</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4007</v>
+        <v>0.0646</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2551</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.948099999999998</v>
+        <v>4.441700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>7.204799999999998</v>
+        <v>8.698500000000001</v>
       </c>
       <c r="F12" t="n">
         <v>-4.2568</v>
@@ -1357,7 +1357,7 @@
         <v>-1.0001</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.091399999999999</v>
+        <v>-3.0914</v>
       </c>
       <c r="I12" t="n">
         <v>2.0916</v>
@@ -1369,7 +1369,7 @@
         <v>2.241699999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9269</v>
+        <v>2.926899999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-6.1685</v>
@@ -1378,7 +1378,7 @@
         <v>-5.333200000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8351999999999999</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="P12" t="n">
         <v>1.1598</v>
@@ -1390,10 +1390,10 @@
         <v>11.5978</v>
       </c>
       <c r="S12" t="n">
-        <v>5.0124</v>
+        <v>6.506</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8729</v>
+        <v>4.3665</v>
       </c>
       <c r="U12" t="n">
         <v>2.1396</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.564</v>
+        <v>8.6813</v>
       </c>
       <c r="E13" t="n">
-        <v>6.819</v>
+        <v>7.6447</v>
       </c>
       <c r="F13" t="n">
-        <v>0.745</v>
+        <v>1.0367</v>
       </c>
       <c r="G13" t="n">
         <v>9.1317</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8565</v>
+        <v>-0.7391</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4778</v>
+        <v>-0.6522</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3787</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>2.1444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.96</v>
+        <v>5.3367</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9454</v>
+        <v>3.3556</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0146</v>
+        <v>1.981</v>
       </c>
       <c r="G14" t="n">
         <v>1.2068</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3589</v>
+        <v>-0.2645</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6335</v>
+        <v>0.0437</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2745</v>
+        <v>-0.3082</v>
       </c>
       <c r="V14" t="n">
         <v>2.5387</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3269</v>
+        <v>0.1079</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9817</v>
+        <v>1.1247</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3452</v>
+        <v>-1.0168</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1683</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2667</v>
+        <v>0.6186</v>
       </c>
       <c r="I15" t="n">
-        <v>0.435</v>
+        <v>0.3144</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9374</v>
+        <v>1.5842</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0295</v>
+        <v>1.1595</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9669</v>
+        <v>0.4247</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.769</v>
+        <v>-0.6512</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2372</v>
+        <v>-0.5409</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5319</v>
+        <v>-0.1103</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8698</v>
+        <v>-0.9307</v>
       </c>
       <c r="T15" t="n">
-        <v>3.539</v>
+        <v>-0.4595</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3308</v>
+        <v>-0.4711</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>-1.7501</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="16">
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. CABOCLO</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2146</v>
+        <v>-0.6377</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4066</v>
+        <v>-0.6132</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8081</v>
+        <v>-0.0245</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3776</v>
+        <v>0.1683</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3241</v>
+        <v>-0.2667</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0535</v>
+        <v>0.435</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0336</v>
+        <v>0.9374</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0336</v>
+        <v>-0.0295</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.9669</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4112</v>
+        <v>-0.769</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3577</v>
+        <v>-0.2372</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0535</v>
+        <v>-0.5319</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7855</v>
+        <v>0.9052</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4402</v>
+        <v>0.944</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3453</v>
+        <v>-0.0389</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3918</v>
+        <v>-1.173</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8538</v>
+        <v>0.9718</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2456</v>
+        <v>-2.1448</v>
       </c>
       <c r="G18" t="n">
         <v>0.149</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3062</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2161</v>
+        <v>-0.0982</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4665</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BERTANS</t>
+          <t>B. CABOCLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.491</v>
+        <v>-1.1918</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1612</v>
+        <v>-0.4066</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6522</v>
+        <v>-0.7852</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3272</v>
+        <v>-0.3776</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1728</v>
+        <v>-0.3241</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1544</v>
+        <v>-0.0535</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7695</v>
+        <v>0.0336</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0168</v>
+        <v>0.0336</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5577</v>
+        <v>-0.4112</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1896</v>
+        <v>-0.3577</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.368</v>
+        <v>-0.0535</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.7625999999999999</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.4402</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.3224</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.2836</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="n">
-        <v>-0.022</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-0.1415</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.1195</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.1418</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.0722</v>
-      </c>
       <c r="X19" t="n">
-        <v>-1.214</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>D. BERTANS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5643</v>
+        <v>-1.4237</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1811</v>
+        <v>0.1612</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7454</v>
+        <v>-1.5849</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9330000000000001</v>
+        <v>-1.3272</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6186</v>
+        <v>-0.1728</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3144</v>
+        <v>-1.1544</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5842</v>
+        <v>-0.7695</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1595</v>
+        <v>0.0168</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4247</v>
+        <v>-0.7863</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6512</v>
+        <v>-0.5577</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5409</v>
+        <v>-0.1896</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1103</v>
+        <v>-0.368</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.6029</v>
+        <v>0.0452</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4031</v>
+        <v>-0.1415</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1997</v>
+        <v>0.1867</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7501</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7501</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.4666</v>
+        <v>-4.8362</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.9149</v>
+        <v>-6.9713</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4483</v>
+        <v>2.1351</v>
       </c>
       <c r="G21" t="n">
         <v>-6.2367</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6089</v>
+        <v>0.0215</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4778</v>
+        <v>-0.5342</v>
       </c>
       <c r="U21" t="n">
-        <v>0.869</v>
+        <v>0.5557</v>
       </c>
       <c r="V21" t="n">
         <v>2.5387</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.4435</v>
+        <v>-6.798</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4019</v>
+        <v>-3.048</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.0416</v>
+        <v>-3.75</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8841</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3634</v>
+        <v>-1.7179</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0886</v>
+        <v>-0.7347</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2748</v>
+        <v>-0.9831</v>
       </c>
       <c r="V22" t="n">
         <v>-2.428</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.947999999999999</v>
+        <v>-2.161599999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>2.506599999999999</v>
+        <v>2.506699999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.454699999999999</v>
+        <v>-4.6683</v>
       </c>
       <c r="G23" t="n">
         <v>1.000000000000001</v>
@@ -2218,16 +2218,16 @@
         <v>3.0914</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0915</v>
+        <v>-2.091500000000001</v>
       </c>
       <c r="J23" t="n">
         <v>6.1686</v>
       </c>
       <c r="K23" t="n">
-        <v>5.333200000000001</v>
+        <v>5.333199999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8355000000000001</v>
+        <v>0.835500000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-5.1684</v>
@@ -2239,7 +2239,7 @@
         <v>-2.9268</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1596</v>
+        <v>-1.159599999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-11.5976</v>
@@ -2248,16 +2248,16 @@
         <v>10.438</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.012599999999999</v>
+        <v>-4.2262</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.1394</v>
+        <v>-2.1396</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.8729</v>
+        <v>-2.0866</v>
       </c>
       <c r="V23" t="n">
-        <v>2.224</v>
+        <v>2.223999999999999</v>
       </c>
       <c r="W23" t="n">
         <v>10.0752</v>
